--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB225832-658C-4B83-8E8B-DB6A3B32B9F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EDA760-8BD0-4068-8DD2-CB61825A64C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="1700" windowWidth="14400" windowHeight="8260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bgm" sheetId="1" r:id="rId1"/>
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EDA760-8BD0-4068-8DD2-CB61825A64C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Bgm" sheetId="1" r:id="rId1"/>
@@ -20,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -40,47 +34,47 @@
     <t>CrossFade</t>
   </si>
   <si>
+    <t>Title</t>
+  </si>
+  <si>
     <t>akaneiro</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Lonely explorer</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Mainmenu</t>
+  </si>
+  <si>
+    <t>BGM34_0</t>
+  </si>
+  <si>
+    <t>Tactics1</t>
+  </si>
+  <si>
+    <t>sabitsuitasekai</t>
   </si>
   <si>
     <t>Battle1</t>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>kotyomusou</t>
   </si>
   <si>
     <t>Boss1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Tactics1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Title</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>kotyomusou</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>Glacial brilliance</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Mainmenu</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -92,27 +86,349 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -120,9 +436,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -134,17 +692,61 @@
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -431,22 +1033,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="11.26953125" customWidth="1"/>
-    <col min="3" max="3" width="42.7265625" customWidth="1"/>
-    <col min="4" max="4" width="7.7265625" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" customWidth="1"/>
+    <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
+    <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="7.72727272727273" customWidth="1"/>
+    <col min="6" max="6" width="10.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,15 +1068,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>0.6</v>
@@ -483,24 +1085,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>100</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1010</v>
       </c>
@@ -508,24 +1110,24 @@
         <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>0.8</v>
       </c>
       <c r="E4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>2010</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -534,15 +1136,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>3010</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -552,8 +1154,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -55,7 +55,7 @@
     <t>Battle1</t>
   </si>
   <si>
-    <t>kotyomusou</t>
+    <t>battle_cry_Re</t>
   </si>
   <si>
     <t>Boss1</t>
@@ -69,9 +69,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -91,12 +91,50 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -105,61 +143,24 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -171,9 +172,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -188,16 +204,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -205,30 +228,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,19 +243,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -267,163 +417,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,21 +434,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -463,15 +448,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -495,6 +471,15 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -503,8 +488,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,145 +542,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1133,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="E5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -43,7 +43,7 @@
     <t>Mainmenu</t>
   </si>
   <si>
-    <t>BGM34_0</t>
+    <t>Deceitful Girl</t>
   </si>
   <si>
     <t>Tactics1</t>
@@ -69,10 +69,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -91,68 +91,61 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -164,32 +157,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -203,32 +210,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,187 +243,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,6 +434,39 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -452,59 +485,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -534,6 +519,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -542,145 +542,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1099,7 +1099,7 @@
         <v>0.8</v>
       </c>
       <c r="E3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -46,10 +46,10 @@
     <t>Deceitful Girl</t>
   </si>
   <si>
-    <t>Tactics1</t>
-  </si>
-  <si>
-    <t>sabitsuitasekai</t>
+    <t>Dungeon1</t>
+  </si>
+  <si>
+    <t>Exploring at sunset</t>
   </si>
   <si>
     <t>Battle1</t>
@@ -71,8 +71,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -91,12 +91,65 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -105,24 +158,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -134,101 +173,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,49 +243,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,127 +417,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,78 +434,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -534,6 +462,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -542,16 +542,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -560,127 +560,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -49,7 +49,7 @@
     <t>Dungeon1</t>
   </si>
   <si>
-    <t>Exploring at sunset</t>
+    <t>tsukihasitteiru</t>
   </si>
   <si>
     <t>Battle1</t>
@@ -70,9 +70,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -97,9 +97,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -114,13 +120,21 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -129,8 +143,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -138,20 +160,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -165,17 +173,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,44 +220,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,181 +249,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,17 +434,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -472,11 +461,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -511,26 +515,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,16 +542,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -560,127 +560,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -61,7 +61,7 @@
     <t>Boss1</t>
   </si>
   <si>
-    <t>Glacial brilliance</t>
+    <t>Truth of Negation</t>
   </si>
 </sst>
 </file>
@@ -69,10 +69,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -91,13 +91,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -105,9 +98,54 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -119,6 +157,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -127,108 +210,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,37 +243,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,145 +393,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,45 +434,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -496,6 +457,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -534,6 +519,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -542,145 +542,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1147,10 +1147,10 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -49,7 +49,7 @@
     <t>Dungeon1</t>
   </si>
   <si>
-    <t>tsukihasitteiru</t>
+    <t>Deserted beach</t>
   </si>
   <si>
     <t>Battle1</t>
@@ -69,10 +69,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -91,6 +91,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -98,12 +105,42 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -112,8 +149,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -126,16 +164,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -148,91 +233,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -243,31 +243,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -279,145 +417,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,15 +434,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -465,7 +456,36 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -500,26 +520,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -542,145 +542,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -69,10 +69,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -90,13 +90,38 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -104,10 +129,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -127,46 +153,60 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -180,22 +220,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -204,33 +228,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -243,6 +243,156 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -255,175 +405,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -481,30 +481,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -534,6 +510,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -542,16 +542,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -560,127 +560,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Id</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>Deserted beach</t>
+  </si>
+  <si>
+    <t>Dungeon2</t>
+  </si>
+  <si>
+    <t>Ruins Investigation</t>
   </si>
   <si>
     <t>Battle1</t>
@@ -69,9 +75,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -90,25 +96,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,14 +150,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,78 +163,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,15 +210,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,187 +249,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,6 +458,54 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -472,15 +526,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -495,45 +540,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -542,7 +548,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -551,7 +557,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -560,127 +566,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1039,8 +1045,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
     <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
@@ -1119,18 +1125,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" customFormat="1" spans="1:5">
       <c r="A5">
-        <v>2010</v>
+        <v>1020</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1138,7 +1144,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
@@ -1147,9 +1153,26 @@
         <v>15</v>
       </c>
       <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>3010</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7">
         <v>0.8</v>
       </c>
-      <c r="E6" t="b">
+      <c r="E7" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Id</t>
   </si>
@@ -56,6 +56,12 @@
   </si>
   <si>
     <t>Ruins Investigation</t>
+  </si>
+  <si>
+    <t>Dungeon21</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_Lost_place_loop</t>
   </si>
   <si>
     <t>Battle1</t>
@@ -76,9 +82,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -104,14 +110,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -125,31 +168,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -164,6 +216,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -172,69 +232,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,187 +255,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,8 +482,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -485,8 +506,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,21 +546,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -548,16 +554,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -566,124 +572,124 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1045,8 +1051,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
     <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
@@ -1144,7 +1150,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
@@ -1153,15 +1159,15 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" customFormat="1" spans="1:5">
       <c r="A7">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>16</v>
@@ -1170,9 +1176,26 @@
         <v>17</v>
       </c>
       <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" spans="1:5">
+      <c r="A8">
+        <v>3010</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8">
         <v>0.8</v>
       </c>
-      <c r="E7" t="b">
+      <c r="E8" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Id</t>
   </si>
@@ -44,6 +44,12 @@
   </si>
   <si>
     <t>Deceitful Girl</t>
+  </si>
+  <si>
+    <t>Interrude</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_Snowy_Day3_loop</t>
   </si>
   <si>
     <t>Dungeon1</t>
@@ -81,10 +87,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -103,7 +109,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,6 +153,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -123,33 +176,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -168,79 +199,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,13 +261,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -273,169 +429,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -460,54 +466,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -538,6 +496,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -546,6 +537,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -554,145 +560,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1051,8 +1057,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="5"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
     <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
@@ -1116,7 +1122,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>1010</v>
+        <v>110</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>10</v>
@@ -1131,14 +1137,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:5">
+    <row r="5" spans="1:5">
       <c r="A5">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D5">
@@ -1148,14 +1154,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" customFormat="1" spans="1:5">
       <c r="A6">
-        <v>1210</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
       <c r="D6">
@@ -1165,9 +1171,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="1" spans="1:5">
+    <row r="7" spans="1:5">
       <c r="A7">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>16</v>
@@ -1176,7 +1182,7 @@
         <v>17</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1184,7 +1190,7 @@
     </row>
     <row r="8" customFormat="1" spans="1:5">
       <c r="A8">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>18</v>
@@ -1193,9 +1199,26 @@
         <v>19</v>
       </c>
       <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:5">
+      <c r="A9">
+        <v>3010</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9">
         <v>0.8</v>
       </c>
-      <c r="E8" t="b">
+      <c r="E9" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Id</t>
   </si>
@@ -62,6 +62,12 @@
   </si>
   <si>
     <t>Ruins Investigation</t>
+  </si>
+  <si>
+    <t>Dungeon3</t>
+  </si>
+  <si>
+    <t>Sunset</t>
   </si>
   <si>
     <t>Dungeon21</t>
@@ -88,9 +94,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -109,30 +115,51 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -141,13 +168,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -169,13 +189,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -184,6 +197,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -191,62 +236,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,25 +267,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,157 +405,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,21 +476,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -504,25 +495,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -552,6 +534,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -560,145 +566,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1057,7 +1063,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1171,14 +1177,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" customFormat="1" spans="1:5">
       <c r="A7">
-        <v>1210</v>
+        <v>1030</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>17</v>
       </c>
       <c r="D7">
@@ -1188,9 +1194,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" customFormat="1" spans="1:5">
+    <row r="8" spans="1:5">
       <c r="A8">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>18</v>
@@ -1199,7 +1205,7 @@
         <v>19</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1207,7 +1213,7 @@
     </row>
     <row r="9" customFormat="1" spans="1:5">
       <c r="A9">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -1216,9 +1222,26 @@
         <v>21</v>
       </c>
       <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:5">
+      <c r="A10">
+        <v>3010</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
         <v>0.8</v>
       </c>
-      <c r="E9" t="b">
+      <c r="E10" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -86,6 +86,12 @@
   </si>
   <si>
     <t>Truth of Negation</t>
+  </si>
+  <si>
+    <t>Boss2</t>
+  </si>
+  <si>
+    <t>Isolation of Hero</t>
   </si>
 </sst>
 </file>
@@ -94,9 +100,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -115,22 +121,121 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -144,15 +249,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -160,99 +259,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -267,187 +273,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,6 +464,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -476,20 +491,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -509,41 +521,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -558,6 +535,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -566,145 +572,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1063,7 +1069,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1245,6 +1251,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <v>3020</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>0.9</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
@@ -52,6 +52,12 @@
     <t>PerituneMaterial_Snowy_Day3_loop</t>
   </si>
   <si>
+    <t>Mainmenu2</t>
+  </si>
+  <si>
+    <t>kiritomichibiki_loop</t>
+  </si>
+  <si>
     <t>Dungeon1</t>
   </si>
   <si>
@@ -80,6 +86,12 @@
   </si>
   <si>
     <t>battle_cry_Re</t>
+  </si>
+  <si>
+    <t>Battle2</t>
+  </si>
+  <si>
+    <t>kakusei</t>
   </si>
   <si>
     <t>Boss1</t>
@@ -99,8 +111,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -121,16 +133,122 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -150,115 +268,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,25 +285,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,157 +459,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,15 +476,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -507,21 +510,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -536,13 +524,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -560,7 +552,27 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,7 +584,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -581,7 +593,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -590,127 +602,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1069,7 +1081,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1151,7 +1163,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>1010</v>
+        <v>120</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>12</v>
@@ -1166,14 +1178,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="1" spans="1:5">
+    <row r="6" spans="1:5">
       <c r="A6">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D6">
@@ -1185,7 +1197,7 @@
     </row>
     <row r="7" customFormat="1" spans="1:5">
       <c r="A7">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>16</v>
@@ -1200,14 +1212,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" customFormat="1" spans="1:5">
       <c r="A8">
-        <v>1210</v>
+        <v>1030</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>19</v>
       </c>
       <c r="D8">
@@ -1217,9 +1229,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="1" spans="1:5">
+    <row r="9" spans="1:5">
       <c r="A9">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -1228,7 +1240,7 @@
         <v>21</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1236,7 +1248,7 @@
     </row>
     <row r="10" customFormat="1" spans="1:5">
       <c r="A10">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>22</v>
@@ -1245,26 +1257,60 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" customFormat="1" spans="1:5">
       <c r="A11">
+        <v>2020</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11">
+        <v>0.8</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:5">
+      <c r="A12">
+        <v>3010</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12">
+        <v>0.8</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:5">
+      <c r="A13">
         <v>3020</v>
       </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11">
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
         <v>0.9</v>
       </c>
-      <c r="E11" t="b">
+      <c r="E13" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -74,6 +74,12 @@
   </si>
   <si>
     <t>Sunset</t>
+  </si>
+  <si>
+    <t>Dungeon4</t>
+  </si>
+  <si>
+    <t>Silent Trigger</t>
   </si>
   <si>
     <t>Dungeon21</t>
@@ -112,8 +118,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -140,7 +146,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,21 +167,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -177,68 +175,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,6 +198,59 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -261,16 +260,23 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -285,13 +291,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,169 +465,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,32 +485,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -525,6 +519,41 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -539,40 +568,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -584,16 +590,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -602,127 +608,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1081,7 +1087,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1229,14 +1235,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" customFormat="1" spans="1:5">
       <c r="A9">
-        <v>1210</v>
+        <v>1040</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>21</v>
       </c>
       <c r="D9">
@@ -1246,9 +1252,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="1" spans="1:5">
+    <row r="10" spans="1:5">
       <c r="A10">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>22</v>
@@ -1257,7 +1263,7 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1265,7 +1271,7 @@
     </row>
     <row r="11" customFormat="1" spans="1:5">
       <c r="A11">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -1274,7 +1280,7 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1282,7 +1288,7 @@
     </row>
     <row r="12" customFormat="1" spans="1:5">
       <c r="A12">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
@@ -1299,18 +1305,35 @@
     </row>
     <row r="13" customFormat="1" spans="1:5">
       <c r="A13">
+        <v>3010</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>0.8</v>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" spans="1:5">
+      <c r="A14">
         <v>3020</v>
       </c>
-      <c r="B13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13">
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
         <v>0.9</v>
       </c>
-      <c r="E13" t="b">
+      <c r="E14" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Id</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>Silent Trigger</t>
+  </si>
+  <si>
+    <t>Dungeon5</t>
+  </si>
+  <si>
+    <t>Hyouketu no Alcadia</t>
   </si>
   <si>
     <t>Dungeon21</t>
@@ -118,8 +124,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -139,14 +145,113 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -154,22 +259,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,13 +272,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -198,85 +280,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,187 +297,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -490,30 +496,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -535,11 +517,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -547,8 +527,23 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,17 +563,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,16 +596,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -608,127 +614,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1087,7 +1093,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1252,14 +1258,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" customFormat="1" spans="1:5">
       <c r="A10">
-        <v>1210</v>
+        <v>1050</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>23</v>
       </c>
       <c r="D10">
@@ -1269,9 +1275,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:5">
+    <row r="11" spans="1:5">
       <c r="A11">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -1280,7 +1286,7 @@
         <v>25</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1288,7 +1294,7 @@
     </row>
     <row r="12" customFormat="1" spans="1:5">
       <c r="A12">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
@@ -1297,7 +1303,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -1305,7 +1311,7 @@
     </row>
     <row r="13" customFormat="1" spans="1:5">
       <c r="A13">
-        <v>3010</v>
+        <v>2020</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -1322,18 +1328,35 @@
     </row>
     <row r="14" customFormat="1" spans="1:5">
       <c r="A14">
+        <v>3010</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>0.8</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:5">
+      <c r="A15">
         <v>3020</v>
       </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14">
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15">
         <v>0.9</v>
       </c>
-      <c r="E14" t="b">
+      <c r="E15" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -123,10 +123,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -145,6 +145,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -152,28 +190,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -181,23 +211,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -211,64 +227,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -282,6 +244,44 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -297,187 +297,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,6 +500,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -515,11 +524,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -527,8 +542,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -563,21 +578,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -596,145 +596,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>Id</t>
   </si>
@@ -116,6 +116,18 @@
   </si>
   <si>
     <t>Isolation of Hero</t>
+  </si>
+  <si>
+    <t>Event1</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_Entangle_loop</t>
+  </si>
+  <si>
+    <t>Event2</t>
+  </si>
+  <si>
+    <t>Event_darkfnt2_mvt</t>
   </si>
 </sst>
 </file>
@@ -123,10 +135,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -145,17 +157,100 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -167,53 +262,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,62 +285,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,181 +309,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,24 +500,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -520,6 +514,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -548,32 +581,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,145 +608,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1093,7 +1105,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1360,6 +1372,40 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="1:5">
+      <c r="A16">
+        <v>4010</v>
+      </c>
+      <c r="B16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16">
+        <v>0.9</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>4020</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17">
+        <v>0.9</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\hibikake_unity\Assets\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5C9132-984B-489C-BFCE-C83BAD63E3B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="11620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="Bgm" sheetId="1" r:id="rId1"/>
@@ -43,6 +37,9 @@
     <t>Title</t>
   </si>
   <si>
+    <t>Inochi_Nakimonono_Uta</t>
+  </si>
+  <si>
     <t>Mainmenu</t>
   </si>
   <si>
@@ -131,17 +128,19 @@
   </si>
   <si>
     <t>Event_darkfnt2_mvt</t>
-  </si>
-  <si>
-    <t>Inochi_Nakimonono_Uta</t>
-    <phoneticPr fontId="3"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,30 +156,345 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -188,34 +502,317 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -502,22 +1099,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
-    <col min="2" max="2" width="11.26953125" customWidth="1"/>
-    <col min="3" max="3" width="42.7265625" customWidth="1"/>
-    <col min="4" max="4" width="7.7265625" customWidth="1"/>
-    <col min="6" max="6" width="10.6328125" customWidth="1"/>
+    <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
+    <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
+    <col min="4" max="4" width="7.72727272727273" customWidth="1"/>
+    <col min="6" max="6" width="10.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,15 +1134,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>37</v>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -554,15 +1151,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>100</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3">
         <v>0.6</v>
@@ -571,15 +1168,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>110</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>0.8</v>
@@ -588,32 +1185,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>120</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1010</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -622,15 +1219,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1020</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>0.6</v>
@@ -639,15 +1236,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1030</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8">
         <v>0.6</v>
@@ -656,15 +1253,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1040</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9">
         <v>0.6</v>
@@ -673,15 +1270,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1050</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>0.6</v>
@@ -690,32 +1287,32 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1210</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>2010</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12">
         <v>0.8</v>
@@ -724,15 +1321,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>2020</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>0.6</v>
@@ -741,15 +1338,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>3010</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -758,15 +1355,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>3020</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>0.6</v>
@@ -775,15 +1372,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>4010</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16">
         <v>0.6</v>
@@ -792,15 +1389,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>4020</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17">
         <v>0.6</v>
@@ -810,8 +1407,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Id</t>
   </si>
@@ -104,6 +104,12 @@
   </si>
   <si>
     <t>kakusei</t>
+  </si>
+  <si>
+    <t>Battle3</t>
+  </si>
+  <si>
+    <t>CODE FROST</t>
   </si>
   <si>
     <t>Boss1</t>
@@ -135,9 +141,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -156,6 +162,74 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -164,45 +238,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -216,66 +254,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -284,9 +262,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,7 +271,36 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,25 +315,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -339,157 +483,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,69 +506,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -590,6 +533,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -600,6 +558,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -608,16 +614,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -626,127 +632,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1105,7 +1111,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1338,9 +1344,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" customFormat="1" spans="1:5">
       <c r="A14">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>30</v>
@@ -1349,7 +1355,7 @@
         <v>31</v>
       </c>
       <c r="D14">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -1357,12 +1363,12 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>3020</v>
-      </c>
-      <c r="B15" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D15">
@@ -1374,7 +1380,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -1391,7 +1397,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -1403,6 +1409,23 @@
         <v>0.6</v>
       </c>
       <c r="E17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>4020</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18">
+        <v>0.6</v>
+      </c>
+      <c r="E18" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Id</t>
   </si>
@@ -112,6 +112,12 @@
     <t>CODE FROST</t>
   </si>
   <si>
+    <t>Battle4</t>
+  </si>
+  <si>
+    <t>Twin_Crystal</t>
+  </si>
+  <si>
     <t>Boss1</t>
   </si>
   <si>
@@ -121,7 +127,7 @@
     <t>Boss2</t>
   </si>
   <si>
-    <t>Isolation of Hero</t>
+    <t>Gracefall</t>
   </si>
   <si>
     <t>Event1</t>
@@ -142,9 +148,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -163,6 +169,65 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -171,62 +236,48 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -238,69 +289,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -315,31 +321,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -351,25 +429,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,115 +495,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,30 +512,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -548,13 +530,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -577,23 +563,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,6 +577,41 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -614,145 +620,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1111,7 +1117,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1287,7 +1293,7 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -1361,9 +1367,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" customFormat="1" spans="1:5">
       <c r="A15">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -1380,12 +1386,12 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>3020</v>
-      </c>
-      <c r="B16" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D16">
@@ -1397,7 +1403,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -1414,7 +1420,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
@@ -1426,6 +1432,23 @@
         <v>0.6</v>
       </c>
       <c r="E18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>4020</v>
+      </c>
+      <c r="B19" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19">
+        <v>0.6</v>
+      </c>
+      <c r="E19" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Event_darkfnt2_mvt</t>
+  </si>
+  <si>
+    <t>Ending</t>
   </si>
 </sst>
 </file>
@@ -148,9 +151,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -165,80 +168,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -250,6 +179,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -258,16 +226,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -281,6 +242,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -289,24 +264,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -321,187 +324,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,21 +515,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -545,35 +533,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,6 +565,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -604,11 +585,33 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,145 +623,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1117,7 +1120,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1452,6 +1455,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>5010</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>0.6</v>
+      </c>
+      <c r="E20" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>Id</t>
   </si>
@@ -88,6 +88,12 @@
     <t>Hyouketu no Alcadia</t>
   </si>
   <si>
+    <t>Dungeon6</t>
+  </si>
+  <si>
+    <t>Gravity of Doom</t>
+  </si>
+  <si>
     <t>Dungeon21</t>
   </si>
   <si>
@@ -128,6 +134,12 @@
   </si>
   <si>
     <t>Gracefall</t>
+  </si>
+  <si>
+    <t>Boss3</t>
+  </si>
+  <si>
+    <t>horobiyukuhikari</t>
   </si>
   <si>
     <t>Event1</t>
@@ -150,10 +162,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -168,6 +180,35 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -179,8 +220,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -188,39 +282,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,74 +304,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,181 +336,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -515,6 +527,30 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -533,17 +569,37 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -565,56 +621,12 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -623,145 +635,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1120,7 +1132,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1302,9 +1314,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" customFormat="1" spans="1:5">
       <c r="A11">
-        <v>1210</v>
+        <v>1060</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>24</v>
@@ -1321,7 +1333,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
@@ -1330,7 +1342,7 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -1338,7 +1350,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
@@ -1347,15 +1359,15 @@
         <v>29</v>
       </c>
       <c r="D13">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="1" spans="1:5">
+    <row r="14" spans="1:5">
       <c r="A14">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>30</v>
@@ -1364,7 +1376,7 @@
         <v>31</v>
       </c>
       <c r="D14">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
@@ -1372,7 +1384,7 @@
     </row>
     <row r="15" customFormat="1" spans="1:5">
       <c r="A15">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -1381,15 +1393,15 @@
         <v>33</v>
       </c>
       <c r="D15">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" customFormat="1" spans="1:5">
       <c r="A16">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>34</v>
@@ -1406,12 +1418,12 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>3020</v>
-      </c>
-      <c r="B17" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D17">
@@ -1423,7 +1435,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B18" t="s">
         <v>38</v>
@@ -1438,9 +1450,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" customFormat="1" spans="1:5">
       <c r="A19">
-        <v>4020</v>
+        <v>3030</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
@@ -1457,18 +1469,52 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>9</v>
+      <c r="C20" t="s">
+        <v>43</v>
       </c>
       <c r="D20">
         <v>0.6</v>
       </c>
       <c r="E20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>4020</v>
+      </c>
+      <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D21">
+        <v>0.6</v>
+      </c>
+      <c r="E21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>5010</v>
+      </c>
+      <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22">
+        <v>0.6</v>
+      </c>
+      <c r="E22" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>Id</t>
   </si>
@@ -137,9 +137,6 @@
   </si>
   <si>
     <t>Boss3</t>
-  </si>
-  <si>
-    <t>horobiyukuhikari</t>
   </si>
   <si>
     <t>Event1</t>
@@ -162,10 +159,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -183,6 +180,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -205,8 +217,55 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,108 +279,46 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -336,187 +333,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -554,21 +551,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -587,8 +569,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -622,8 +619,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -635,145 +632,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1458,7 +1455,7 @@
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19">
         <v>0.6</v>
@@ -1472,10 +1469,10 @@
         <v>4010</v>
       </c>
       <c r="B20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" t="s">
         <v>42</v>
-      </c>
-      <c r="C20" t="s">
-        <v>43</v>
       </c>
       <c r="D20">
         <v>0.6</v>
@@ -1489,10 +1486,10 @@
         <v>4020</v>
       </c>
       <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="s">
         <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>45</v>
       </c>
       <c r="D21">
         <v>0.6</v>
@@ -1506,7 +1503,7 @@
         <v>5010</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>9</v>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>Id</t>
   </si>
@@ -98,6 +98,12 @@
   </si>
   <si>
     <t>PerituneMaterial_Lost_place_loop</t>
+  </si>
+  <si>
+    <t>DungeonClear</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_Soaring</t>
   </si>
   <si>
     <t>Battle1</t>
@@ -159,9 +165,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -180,14 +186,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -195,24 +231,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,47 +248,53 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,9 +308,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,31 +323,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,6 +339,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -345,13 +375,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,73 +465,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,19 +483,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,55 +519,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,6 +530,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -546,7 +591,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,30 +622,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -600,30 +630,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -632,16 +638,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -650,127 +656,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1129,7 +1135,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1339,32 +1345,32 @@
         <v>27</v>
       </c>
       <c r="D12">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" customFormat="1" spans="1:5">
       <c r="A13">
-        <v>2010</v>
+        <v>1510</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>29</v>
       </c>
       <c r="D13">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>30</v>
@@ -1373,15 +1379,15 @@
         <v>31</v>
       </c>
       <c r="D14">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="1" spans="1:5">
+    <row r="15" spans="1:5">
       <c r="A15">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
@@ -1390,7 +1396,7 @@
         <v>33</v>
       </c>
       <c r="D15">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -1398,7 +1404,7 @@
     </row>
     <row r="16" customFormat="1" spans="1:5">
       <c r="A16">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>34</v>
@@ -1407,15 +1413,15 @@
         <v>35</v>
       </c>
       <c r="D16">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" customFormat="1" spans="1:5">
       <c r="A17">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>36</v>
@@ -1432,12 +1438,12 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>3020</v>
-      </c>
-      <c r="B18" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D18">
@@ -1447,15 +1453,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="1" spans="1:5">
+    <row r="19" spans="1:5">
       <c r="A19">
-        <v>3030</v>
+        <v>3020</v>
       </c>
       <c r="B19" t="s">
         <v>40</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D19">
         <v>0.6</v>
@@ -1464,15 +1470,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" customFormat="1" spans="1:5">
       <c r="A20">
-        <v>4010</v>
+        <v>3030</v>
       </c>
       <c r="B20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" t="s">
         <v>41</v>
-      </c>
-      <c r="C20" t="s">
-        <v>42</v>
       </c>
       <c r="D20">
         <v>0.6</v>
@@ -1483,7 +1489,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>4020</v>
+        <v>4010</v>
       </c>
       <c r="B21" t="s">
         <v>43</v>
@@ -1500,18 +1506,35 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>5010</v>
+        <v>4020</v>
       </c>
       <c r="B22" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>9</v>
+      <c r="C22" t="s">
+        <v>46</v>
       </c>
       <c r="D22">
         <v>0.6</v>
       </c>
       <c r="E22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>5010</v>
+      </c>
+      <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>0.6</v>
+      </c>
+      <c r="E23" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -186,20 +186,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -208,24 +194,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,9 +233,47 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -247,7 +285,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -255,46 +292,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,14 +309,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,187 +339,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -533,41 +533,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,20 +557,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,6 +597,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -638,7 +638,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -647,7 +647,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -656,25 +656,25 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -683,100 +683,100 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -165,9 +165,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -186,6 +186,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -194,6 +209,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -203,75 +263,60 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -284,51 +329,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -339,13 +339,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -357,37 +465,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,127 +507,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,6 +530,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -557,17 +566,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,31 +601,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,16 +638,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -656,127 +656,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="Bgm" sheetId="1" r:id="rId1"/>
@@ -186,18 +186,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -209,82 +233,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -293,30 +241,51 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,6 +298,37 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -339,187 +339,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,24 +530,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -566,6 +548,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -577,11 +598,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,32 +620,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,7 +638,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -647,7 +647,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -656,127 +656,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
   <si>
     <t>Id</t>
   </si>
@@ -56,6 +56,18 @@
   </si>
   <si>
     <t>kiritomichibiki_loop</t>
+  </si>
+  <si>
+    <t>Relief1</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_World_OP2_Musicbox_loop</t>
+  </si>
+  <si>
+    <t>Relief2</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_World_OP2</t>
   </si>
   <si>
     <t>Dungeon1</t>
@@ -165,10 +177,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -186,6 +198,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -194,6 +220,89 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -202,24 +311,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,97 +328,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,187 +351,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,16 +560,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -598,30 +619,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -630,6 +627,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -638,145 +650,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1135,7 +1147,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1234,7 +1246,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>1010</v>
+        <v>210</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>14</v>
@@ -1249,14 +1261,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" customFormat="1" spans="1:5">
       <c r="A7">
-        <v>1020</v>
+        <v>220</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D7">
@@ -1268,12 +1280,12 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D8">
@@ -1285,7 +1297,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>1040</v>
+        <v>1020</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>20</v>
@@ -1302,7 +1314,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>1050</v>
+        <v>1030</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>22</v>
@@ -1311,24 +1323,24 @@
         <v>23</v>
       </c>
       <c r="D10">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="1" spans="1:5">
+    <row r="11" spans="1:5">
       <c r="A11">
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -1336,16 +1348,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>1210</v>
+        <v>1050</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>27</v>
       </c>
       <c r="D12">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="E12" t="b">
         <v>0</v>
@@ -1353,24 +1365,24 @@
     </row>
     <row r="13" customFormat="1" spans="1:5">
       <c r="A13">
-        <v>1510</v>
+        <v>1060</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D13">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>30</v>
@@ -1379,32 +1391,32 @@
         <v>31</v>
       </c>
       <c r="D14">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" customFormat="1" spans="1:5">
       <c r="A15">
-        <v>2020</v>
+        <v>1510</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>33</v>
       </c>
       <c r="D15">
         <v>0.6</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="1" spans="1:5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>34</v>
@@ -1419,9 +1431,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="1:5">
+    <row r="17" spans="1:5">
       <c r="A17">
-        <v>2040</v>
+        <v>2020</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>36</v>
@@ -1436,9 +1448,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" customFormat="1" spans="1:5">
       <c r="A18">
-        <v>3010</v>
+        <v>2030</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>38</v>
@@ -1447,20 +1459,20 @@
         <v>39</v>
       </c>
       <c r="D18">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" customFormat="1" spans="1:5">
       <c r="A19">
-        <v>3020</v>
-      </c>
-      <c r="B19" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D19">
@@ -1470,15 +1482,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" customFormat="1" spans="1:5">
+    <row r="20" spans="1:5">
       <c r="A20">
-        <v>3030</v>
-      </c>
-      <c r="B20" t="s">
+        <v>3010</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" t="s">
-        <v>41</v>
+      <c r="C20" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="D20">
         <v>0.6</v>
@@ -1489,13 +1501,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>4010</v>
+        <v>3020</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21">
         <v>0.6</v>
@@ -1504,15 +1516,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" customFormat="1" spans="1:5">
       <c r="A22">
-        <v>4020</v>
+        <v>3030</v>
       </c>
       <c r="B22" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" t="s">
         <v>45</v>
-      </c>
-      <c r="C22" t="s">
-        <v>46</v>
       </c>
       <c r="D22">
         <v>0.6</v>
@@ -1523,18 +1535,52 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>5010</v>
+        <v>4010</v>
       </c>
       <c r="B23" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23">
+        <v>0.6</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>4020</v>
+      </c>
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>0.6</v>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>5010</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D23">
-        <v>0.6</v>
-      </c>
-      <c r="E23" t="b">
+      <c r="D25">
+        <v>0.6</v>
+      </c>
+      <c r="E25" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>Id</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t>CrossFade</t>
+  </si>
+  <si>
+    <t>ResourceType</t>
   </si>
   <si>
     <t>Title</t>
@@ -177,10 +180,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -198,6 +201,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -205,31 +230,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -252,9 +300,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -267,76 +323,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,19 +354,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,25 +498,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,133 +522,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,6 +545,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -560,11 +572,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,43 +605,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,6 +625,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -650,16 +653,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -668,127 +671,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1147,8 +1150,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="5"/>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
     <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
@@ -1156,7 +1159,7 @@
     <col min="6" max="6" width="10.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1175,16 +1178,19 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1192,16 +1198,19 @@
       <c r="E2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>100</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>0.6</v>
@@ -1209,16 +1218,19 @@
       <c r="E3" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>110</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4">
         <v>0.8</v>
@@ -1226,16 +1238,19 @@
       <c r="E4" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>120</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5">
         <v>0.6</v>
@@ -1243,16 +1258,19 @@
       <c r="E5" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>210</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>0.6</v>
@@ -1260,16 +1278,19 @@
       <c r="E6" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:5">
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:7">
       <c r="A7">
         <v>220</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D7">
         <v>0.6</v>
@@ -1277,16 +1298,19 @@
       <c r="E7" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>1010</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8">
         <v>0.6</v>
@@ -1294,16 +1318,19 @@
       <c r="E8" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>1020</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>0.6</v>
@@ -1311,16 +1338,19 @@
       <c r="E9" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>1030</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>0.6</v>
@@ -1328,16 +1358,19 @@
       <c r="E10" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>1040</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>0.6</v>
@@ -1345,16 +1378,19 @@
       <c r="E11" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>1050</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>0.7</v>
@@ -1362,16 +1398,19 @@
       <c r="E12" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" customFormat="1" spans="1:5">
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" spans="1:7">
       <c r="A13">
         <v>1060</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>0.5</v>
@@ -1379,16 +1418,19 @@
       <c r="E13" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>1210</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -1396,16 +1438,19 @@
       <c r="E14" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" customFormat="1" spans="1:5">
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" spans="1:7">
       <c r="A15">
         <v>1510</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15">
         <v>0.6</v>
@@ -1413,16 +1458,19 @@
       <c r="E15" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>2010</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>0.8</v>
@@ -1430,16 +1478,19 @@
       <c r="E16" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>2020</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>0.6</v>
@@ -1447,16 +1498,19 @@
       <c r="E17" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" customFormat="1" spans="1:5">
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:7">
       <c r="A18">
         <v>2030</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18">
         <v>0.8</v>
@@ -1464,16 +1518,19 @@
       <c r="E18" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" customFormat="1" spans="1:5">
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:7">
       <c r="A19">
         <v>2040</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D19">
         <v>0.6</v>
@@ -1481,16 +1538,19 @@
       <c r="E19" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>3010</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D20">
         <v>0.6</v>
@@ -1498,16 +1558,19 @@
       <c r="E20" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>3020</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D21">
         <v>0.6</v>
@@ -1515,33 +1578,39 @@
       <c r="E21" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" customFormat="1" spans="1:5">
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" spans="1:7">
       <c r="A22">
         <v>3030</v>
       </c>
       <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" t="s">
         <v>46</v>
       </c>
-      <c r="C22" t="s">
-        <v>45</v>
-      </c>
       <c r="D22">
         <v>0.6</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>4010</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23">
         <v>0.6</v>
@@ -1549,16 +1618,19 @@
       <c r="E23" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>4020</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24">
         <v>0.6</v>
@@ -1566,22 +1638,28 @@
       <c r="E24" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>5010</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D25">
         <v>0.6</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -76,7 +76,7 @@
     <t>Dungeon1</t>
   </si>
   <si>
-    <t>Deserted beach</t>
+    <t>Neural Rebellion</t>
   </si>
   <si>
     <t>Dungeon2</t>
@@ -124,7 +124,7 @@
     <t>Battle1</t>
   </si>
   <si>
-    <t>battle_cry_Re</t>
+    <t>Crystal Afterimage</t>
   </si>
   <si>
     <t>Battle2</t>
@@ -181,8 +181,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -201,83 +201,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -298,6 +245,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -322,8 +313,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,7 +323,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,187 +354,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -551,8 +551,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,30 +587,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -637,6 +613,30 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -653,7 +653,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -662,7 +662,7 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -671,127 +671,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -124,7 +124,7 @@
     <t>Battle1</t>
   </si>
   <si>
-    <t>Crystal Afterimage</t>
+    <t>battle_cry_Re</t>
   </si>
   <si>
     <t>Battle2</t>
@@ -182,8 +182,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -202,6 +202,29 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -209,22 +232,67 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,60 +306,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -315,31 +332,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,31 +354,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -390,31 +456,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,115 +534,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,9 +550,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -568,21 +570,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -605,8 +592,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,6 +618,15 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,17 +645,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -659,139 +659,139 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="19200" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Bgm" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
     <t>Battle1</t>
   </si>
   <si>
-    <t>battle_cry_Re</t>
+    <t>Astral_Wind</t>
   </si>
   <si>
     <t>Battle2</t>
@@ -180,10 +180,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -202,6 +202,43 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -210,91 +247,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -306,19 +269,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -330,16 +285,61 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,25 +354,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,19 +522,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -408,133 +534,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -550,11 +550,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -574,17 +602,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,34 +620,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -653,145 +653,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -811,12 +811,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -1473,10 +1473,10 @@
         <v>36</v>
       </c>
       <c r="D16">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>1</v>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -180,10 +180,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -201,6 +201,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -209,7 +232,75 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -224,60 +315,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -285,6 +322,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -292,54 +330,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -354,6 +354,120 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -366,31 +480,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,139 +516,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,30 +545,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -583,6 +559,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,21 +607,25 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -653,145 +653,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1473,7 +1473,7 @@
         <v>36</v>
       </c>
       <c r="D16">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Bgm" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
   <si>
     <t>Id</t>
   </si>
@@ -169,7 +169,31 @@
     <t>Event2</t>
   </si>
   <si>
-    <t>Event_darkfnt2_mvt</t>
+    <t>fuon2</t>
+  </si>
+  <si>
+    <t>2-22 The Crumbling Id</t>
+  </si>
+  <si>
+    <t>ポケットサウンド</t>
+  </si>
+  <si>
+    <t>Event3</t>
+  </si>
+  <si>
+    <t>natuwasucinema</t>
+  </si>
+  <si>
+    <t>1-10 When a Person Is No Longer a Person</t>
+  </si>
+  <si>
+    <t>Event4</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_Elysium</t>
+  </si>
+  <si>
+    <t>1-09 The Road to Glory and Prosperity</t>
   </si>
   <si>
     <t>Ending</t>
@@ -180,10 +204,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -198,6 +222,65 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -209,25 +292,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -238,8 +307,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,77 +355,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -337,13 +368,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -360,19 +384,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,13 +504,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,13 +546,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -420,121 +558,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -563,26 +587,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -602,7 +606,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,6 +639,17 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -653,7 +677,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -662,13 +686,13 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -677,121 +701,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1150,8 +1174,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="6"/>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
     <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
@@ -1622,7 +1646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:9">
       <c r="A24">
         <v>4020</v>
       </c>
@@ -1641,24 +1665,79 @@
       <c r="G24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" t="s">
+        <v>52</v>
+      </c>
+      <c r="I24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25">
+        <v>4030</v>
+      </c>
+      <c r="B25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25">
+        <v>0.5</v>
+      </c>
+      <c r="E25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26">
+        <v>4040</v>
+      </c>
+      <c r="B26" t="s">
+        <v>57</v>
+      </c>
+      <c r="C26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D26">
+        <v>0.5</v>
+      </c>
+      <c r="E26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
         <v>5010</v>
       </c>
-      <c r="B25" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="B27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D25">
+      <c r="D27">
         <v>0.6</v>
       </c>
-      <c r="E25" t="b">
-        <v>0</v>
-      </c>
-      <c r="G25">
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -82,7 +82,7 @@
     <t>Dungeon2</t>
   </si>
   <si>
-    <t>Ruins Investigation</t>
+    <t>Ice of the spring river</t>
   </si>
   <si>
     <t>Dungeon3</t>
@@ -204,10 +204,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -222,6 +222,29 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -233,6 +256,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -241,49 +309,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -292,11 +317,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,30 +348,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -360,14 +368,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -378,31 +378,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -414,151 +558,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,6 +569,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -587,6 +596,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -598,15 +631,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,15 +661,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -654,21 +669,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -677,7 +677,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -686,136 +686,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1357,7 +1357,7 @@
         <v>22</v>
       </c>
       <c r="D9">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
   <si>
     <t>Id</t>
   </si>
@@ -194,6 +194,15 @@
   </si>
   <si>
     <t>1-09 The Road to Glory and Prosperity</t>
+  </si>
+  <si>
+    <t>Event5</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_Strategy4_loop</t>
+  </si>
+  <si>
+    <t>王城のイメージ</t>
   </si>
   <si>
     <t>Ending</t>
@@ -204,10 +213,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -225,6 +234,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -240,6 +318,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -248,14 +333,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -265,109 +342,41 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -378,24 +387,168 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -408,157 +561,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,15 +578,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -592,30 +592,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,16 +620,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -669,6 +645,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -677,145 +686,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1174,7 +1183,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1721,23 +1730,46 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:8">
       <c r="A27">
-        <v>5010</v>
+        <v>4050</v>
       </c>
       <c r="B27" t="s">
         <v>60</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" t="s">
+        <v>61</v>
+      </c>
+      <c r="D27">
+        <v>0.5</v>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>5010</v>
+      </c>
+      <c r="B28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>0.6</v>
       </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27">
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
   <si>
     <t>Id</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>王城のイメージ</t>
+  </si>
+  <si>
+    <t>Event6</t>
+  </si>
+  <si>
+    <t>lastsummer2</t>
   </si>
   <si>
     <t>Ending</t>
@@ -214,8 +220,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -234,10 +240,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -249,6 +256,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -264,6 +279,103 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -271,112 +383,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -387,19 +393,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,7 +525,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,151 +573,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,6 +584,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -592,6 +607,32 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,59 +652,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -678,6 +666,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -686,145 +692,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1183,7 +1189,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1755,21 +1761,41 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>5010</v>
+        <v>4060</v>
       </c>
       <c r="B28" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28">
+        <v>0.5</v>
+      </c>
+      <c r="E28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>5010</v>
+      </c>
+      <c r="B29" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D28">
+      <c r="D29">
         <v>0.6</v>
       </c>
-      <c r="E28" t="b">
-        <v>0</v>
-      </c>
-      <c r="G28">
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
   <si>
     <t>Id</t>
   </si>
@@ -209,6 +209,15 @@
   </si>
   <si>
     <t>lastsummer2</t>
+  </si>
+  <si>
+    <t>Event7</t>
+  </si>
+  <si>
+    <t>PerituneMaterial_Awayuki</t>
+  </si>
+  <si>
+    <t>倭国の</t>
   </si>
   <si>
     <t>Ending</t>
@@ -219,10 +228,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -237,6 +246,119 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,64 +370,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,67 +387,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -393,187 +402,187 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -587,11 +596,43 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,11 +654,27 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,54 +693,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -692,145 +701,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1189,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1779,23 +1788,46 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:8">
       <c r="A29">
-        <v>5010</v>
+        <v>4070</v>
       </c>
       <c r="B29" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29">
+        <v>0.5</v>
+      </c>
+      <c r="E29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>5010</v>
+      </c>
+      <c r="B30" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <v>0.6</v>
       </c>
-      <c r="E29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29">
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
   <si>
     <t>Id</t>
   </si>
@@ -218,6 +218,15 @@
   </si>
   <si>
     <t>倭国の</t>
+  </si>
+  <si>
+    <t>Event8</t>
+  </si>
+  <si>
+    <t>sentakukiro</t>
+  </si>
+  <si>
+    <t>2-24 Behave irrationally</t>
   </si>
   <si>
     <t>Ending</t>
@@ -229,9 +238,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -250,6 +259,35 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -257,7 +295,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,8 +332,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,100 +382,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -402,91 +411,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -498,7 +567,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -510,66 +585,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -577,12 +592,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -593,6 +602,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -613,56 +661,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
@@ -672,9 +670,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -693,6 +693,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -701,145 +710,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1198,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1811,23 +1820,49 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:9">
       <c r="A30">
-        <v>5010</v>
+        <v>4080</v>
       </c>
       <c r="B30" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30">
+        <v>0.5</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>70</v>
+      </c>
+      <c r="I30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>5010</v>
+      </c>
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>0.6</v>
       </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30">
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -239,8 +239,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -258,8 +258,114 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,73 +379,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -349,30 +388,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -380,21 +395,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -417,13 +417,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,25 +573,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,133 +585,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,17 +620,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,8 +632,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,26 +653,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -694,6 +668,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -702,6 +691,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -710,22 +710,22 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -734,121 +734,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
   <si>
     <t>Id</t>
   </si>
@@ -88,13 +88,10 @@
     <t>Dungeon3</t>
   </si>
   <si>
-    <t>Sunset</t>
+    <t>Silent Trigger</t>
   </si>
   <si>
     <t>Dungeon4</t>
-  </si>
-  <si>
-    <t>Silent Trigger</t>
   </si>
   <si>
     <t>Dungeon5</t>
@@ -238,9 +235,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -255,6 +252,127 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -266,95 +384,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -363,40 +392,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -411,19 +408,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,13 +510,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,145 +558,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,65 +602,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -686,8 +629,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -702,6 +660,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -710,145 +707,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1427,7 +1424,7 @@
         <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>0.6</v>
@@ -1444,10 +1441,10 @@
         <v>1050</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
         <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>28</v>
       </c>
       <c r="D12">
         <v>0.7</v>
@@ -1464,10 +1461,10 @@
         <v>1060</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="D13">
         <v>0.5</v>
@@ -1484,10 +1481,10 @@
         <v>1210</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -1504,10 +1501,10 @@
         <v>1510</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
         <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>34</v>
       </c>
       <c r="D15">
         <v>0.6</v>
@@ -1524,10 +1521,10 @@
         <v>2010</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1544,10 +1541,10 @@
         <v>2020</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="D17">
         <v>0.6</v>
@@ -1564,10 +1561,10 @@
         <v>2030</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="D18">
         <v>0.8</v>
@@ -1584,10 +1581,10 @@
         <v>2040</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="D19">
         <v>0.6</v>
@@ -1604,10 +1601,10 @@
         <v>3010</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D20">
         <v>0.6</v>
@@ -1624,10 +1621,10 @@
         <v>3020</v>
       </c>
       <c r="B21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
         <v>45</v>
-      </c>
-      <c r="C21" t="s">
-        <v>46</v>
       </c>
       <c r="D21">
         <v>0.6</v>
@@ -1644,10 +1641,10 @@
         <v>3030</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <v>0.6</v>
@@ -1664,10 +1661,10 @@
         <v>4010</v>
       </c>
       <c r="B23" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" t="s">
         <v>48</v>
-      </c>
-      <c r="C23" t="s">
-        <v>49</v>
       </c>
       <c r="D23">
         <v>0.6</v>
@@ -1684,10 +1681,10 @@
         <v>4020</v>
       </c>
       <c r="B24" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
         <v>50</v>
-      </c>
-      <c r="C24" t="s">
-        <v>51</v>
       </c>
       <c r="D24">
         <v>0.6</v>
@@ -1699,10 +1696,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
+        <v>51</v>
+      </c>
+      <c r="I24" t="s">
         <v>52</v>
-      </c>
-      <c r="I24" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1710,10 +1707,10 @@
         <v>4030</v>
       </c>
       <c r="B25" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" t="s">
         <v>54</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
       </c>
       <c r="D25">
         <v>0.5</v>
@@ -1725,10 +1722,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1736,10 +1733,10 @@
         <v>4040</v>
       </c>
       <c r="B26" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" t="s">
         <v>57</v>
-      </c>
-      <c r="C26" t="s">
-        <v>58</v>
       </c>
       <c r="D26">
         <v>0.5</v>
@@ -1751,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1759,10 +1756,10 @@
         <v>4050</v>
       </c>
       <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
         <v>60</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
       </c>
       <c r="D27">
         <v>0.5</v>
@@ -1774,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1782,10 +1779,10 @@
         <v>4060</v>
       </c>
       <c r="B28" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" t="s">
         <v>63</v>
-      </c>
-      <c r="C28" t="s">
-        <v>64</v>
       </c>
       <c r="D28">
         <v>0.5</v>
@@ -1802,10 +1799,10 @@
         <v>4070</v>
       </c>
       <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" t="s">
         <v>65</v>
-      </c>
-      <c r="C29" t="s">
-        <v>66</v>
       </c>
       <c r="D29">
         <v>0.5</v>
@@ -1817,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1825,10 +1822,10 @@
         <v>4080</v>
       </c>
       <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
         <v>68</v>
-      </c>
-      <c r="C30" t="s">
-        <v>69</v>
       </c>
       <c r="D30">
         <v>0.5</v>
@@ -1840,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1851,7 +1848,7 @@
         <v>5010</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
   <si>
     <t>Id</t>
   </si>
@@ -91,6 +91,9 @@
     <t>Silent Trigger</t>
   </si>
   <si>
+    <t>Rem chronicle【レムクロニクル】 https://www.youtube.com/@Remchronicle_BGM</t>
+  </si>
+  <si>
     <t>Dungeon4</t>
   </si>
   <si>
@@ -122,6 +125,9 @@
   </si>
   <si>
     <t>Astral_Wind</t>
+  </si>
+  <si>
+    <t>【戦闘音楽工房】</t>
   </si>
   <si>
     <t>Battle2</t>
@@ -234,10 +240,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -255,8 +261,74 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,16 +344,17 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -300,6 +373,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,17 +391,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -331,73 +404,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -408,13 +414,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,49 +570,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -480,115 +594,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -599,6 +605,45 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -635,51 +680,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -707,153 +713,156 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="10" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1396,7 +1405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>1030</v>
       </c>
@@ -1414,6 +1423,9 @@
       </c>
       <c r="G10">
         <v>0</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1421,7 +1433,7 @@
         <v>1040</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -1436,15 +1448,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>1050</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>0.7</v>
@@ -1454,6 +1466,9 @@
       </c>
       <c r="G12">
         <v>0</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="1" spans="1:7">
@@ -1461,10 +1476,10 @@
         <v>1060</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13">
         <v>0.5</v>
@@ -1481,10 +1496,10 @@
         <v>1210</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14">
         <v>0.6</v>
@@ -1501,10 +1516,10 @@
         <v>1510</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15">
         <v>0.6</v>
@@ -1516,15 +1531,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>2010</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1534,6 +1549,9 @@
       </c>
       <c r="G16">
         <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1541,10 +1559,10 @@
         <v>2020</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D17">
         <v>0.6</v>
@@ -1561,10 +1579,10 @@
         <v>2030</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>0.8</v>
@@ -1581,10 +1599,10 @@
         <v>2040</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D19">
         <v>0.6</v>
@@ -1601,10 +1619,10 @@
         <v>3010</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D20">
         <v>0.6</v>
@@ -1621,10 +1639,10 @@
         <v>3020</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D21">
         <v>0.6</v>
@@ -1641,10 +1659,10 @@
         <v>3030</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D22">
         <v>0.6</v>
@@ -1661,10 +1679,10 @@
         <v>4010</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D23">
         <v>0.6</v>
@@ -1681,10 +1699,10 @@
         <v>4020</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D24">
         <v>0.6</v>
@@ -1696,10 +1714,10 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I24" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -1707,10 +1725,10 @@
         <v>4030</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D25">
         <v>0.5</v>
@@ -1722,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I25" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1733,10 +1751,10 @@
         <v>4040</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D26">
         <v>0.5</v>
@@ -1748,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1756,10 +1774,10 @@
         <v>4050</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D27">
         <v>0.5</v>
@@ -1771,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1779,10 +1797,10 @@
         <v>4060</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D28">
         <v>0.5</v>
@@ -1799,10 +1817,10 @@
         <v>4070</v>
       </c>
       <c r="B29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D29">
         <v>0.5</v>
@@ -1814,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -1822,10 +1840,10 @@
         <v>4080</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C30" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D30">
         <v>0.5</v>
@@ -1837,10 +1855,10 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1848,7 +1866,7 @@
         <v>5010</v>
       </c>
       <c r="B31" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>
@@ -1864,6 +1882,10 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H12" r:id="rId1" display="Rem chronicle【レムクロニクル】 https://www.youtube.com/@Remchronicle_BGM"/>
+    <hyperlink ref="H10" r:id="rId1" display="Rem chronicle【レムクロニクル】 https://www.youtube.com/@Remchronicle_BGM"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -230,6 +230,15 @@
   </si>
   <si>
     <t>2-24 Behave irrationally</t>
+  </si>
+  <si>
+    <t>Event9</t>
+  </si>
+  <si>
+    <t>tuyu</t>
+  </si>
+  <si>
+    <t>1-06 All Becomes Twilight</t>
   </si>
   <si>
     <t>Ending</t>
@@ -240,10 +249,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -269,10 +278,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -292,51 +346,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -351,31 +385,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -389,19 +400,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -414,31 +423,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -450,151 +567,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -623,15 +632,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -651,7 +651,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +683,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -705,6 +703,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -713,7 +722,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -722,136 +731,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1213,7 +1222,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
@@ -1861,23 +1870,49 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:9">
       <c r="A31">
-        <v>5010</v>
+        <v>4090</v>
       </c>
       <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31">
+        <v>0.5</v>
+      </c>
+      <c r="E31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>5010</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>0.6</v>
       </c>
-      <c r="E31" t="b">
-        <v>0</v>
-      </c>
-      <c r="G31">
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -249,9 +249,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -278,6 +278,74 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -287,21 +355,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,14 +370,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -330,23 +383,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -368,45 +407,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -429,181 +429,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,63 +628,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -714,6 +657,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -722,145 +722,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -249,10 +249,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -278,6 +278,103 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -288,7 +385,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,22 +399,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,90 +413,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -423,19 +423,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,163 +579,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -628,32 +628,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -682,15 +656,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -710,7 +675,42 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -722,145 +722,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
   <si>
     <t>Id</t>
   </si>
@@ -151,7 +151,7 @@
     <t>Boss1</t>
   </si>
   <si>
-    <t>Truth of Negation</t>
+    <t>raiou_issen</t>
   </si>
   <si>
     <t>Boss2</t>
@@ -250,8 +250,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -285,6 +285,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -293,9 +294,54 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -307,15 +353,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,28 +369,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -359,27 +377,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -393,22 +408,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -429,13 +429,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,163 +591,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -617,17 +617,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -650,8 +646,32 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,28 +694,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -722,145 +722,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>3010</v>
       </c>
@@ -1637,10 +1637,13 @@
         <v>0.6</v>
       </c>
       <c r="E20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:7">

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -249,10 +249,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -285,6 +285,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,8 +315,78 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,17 +400,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -329,90 +413,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -423,25 +423,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -453,157 +603,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -619,10 +619,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -645,8 +643,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -691,15 +691,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -714,6 +705,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -722,145 +722,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1634,7 +1634,7 @@
         <v>45</v>
       </c>
       <c r="D20">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -250,9 +250,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -279,7 +279,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,6 +331,68 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,90 +406,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -391,28 +413,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -423,19 +423,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,163 +597,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -620,8 +620,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,17 +637,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -691,6 +680,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -705,15 +714,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -722,145 +722,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -112,7 +112,7 @@
     <t>Dungeon21</t>
   </si>
   <si>
-    <t>PerituneMaterial_Lost_place_loop</t>
+    <t>Crystal Reverie</t>
   </si>
   <si>
     <t>DungeonClear</t>
@@ -249,10 +249,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -279,9 +279,70 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -292,10 +353,49 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -308,107 +408,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -423,79 +423,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -507,103 +585,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,78 +614,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -714,6 +642,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -722,145 +722,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1225,7 +1225,7 @@
   <dimension ref="A1:I32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="11.2727272727273" customWidth="1"/>
+    <col min="2" max="2" width="15.5727272727273" customWidth="1"/>
     <col min="3" max="3" width="42.7272727272727" customWidth="1"/>
     <col min="4" max="4" width="7.72727272727273" customWidth="1"/>
     <col min="6" max="6" width="10.6363636363636" customWidth="1"/>

--- a/Assets/Data/BGM.xlsx
+++ b/Assets/Data/BGM.xlsx
@@ -250,8 +250,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
@@ -278,8 +278,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,8 +294,106 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,105 +408,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -423,37 +423,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,49 +585,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -519,91 +603,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -614,47 +614,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -706,6 +665,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -714,6 +703,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -722,25 +722,25 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="25" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -749,118 +749,118 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
